--- a/03_Cluster_groups/Muscle_strength/05_Module_Contrasts/c_data/module_contrasts.xlsx
+++ b/03_Cluster_groups/Muscle_strength/05_Module_Contrasts/c_data/module_contrasts.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1357" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1354" uniqueCount="271">
   <si>
     <t>sheet</t>
   </si>
@@ -834,12 +834,6 @@
   </si>
   <si>
     <t>3.0.2</t>
-  </si>
-  <si>
-    <t>writexl</t>
-  </si>
-  <si>
-    <t>2.0.1</t>
   </si>
 </sst>
 </file>
@@ -11958,7 +11952,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C85"/>
+  <dimension ref="A1:C84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -12885,17 +12879,6 @@
         <v>110</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85" t="s">
-        <v>271</v>
-      </c>
-      <c r="B85" t="s">
-        <v>272</v>
-      </c>
-      <c r="C85" t="s">
-        <v>153</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/03_Cluster_groups/Muscle_strength/05_Module_Contrasts/c_data/module_contrasts.xlsx
+++ b/03_Cluster_groups/Muscle_strength/05_Module_Contrasts/c_data/module_contrasts.xlsx
@@ -299,10 +299,10 @@
     <t>modules</t>
   </si>
   <si>
-    <t>03_Cluster_groups/Muscle_strength/01_Clustering/c_data/inputs/modules.rds</t>
-  </si>
-  <si>
-    <t>1e9ff28384188882fe2f63a84381f1b3</t>
+    <t>01_Processing/06_Module_Building/c_data/modules.rds</t>
+  </si>
+  <si>
+    <t>9062a97ff96fac52908895e0eeb7bf57</t>
   </si>
   <si>
     <t>design</t>
@@ -311,7 +311,7 @@
     <t>03_Cluster_groups/Muscle_strength/02_Design_Contrasts/c_data/design.rds</t>
   </si>
   <si>
-    <t>7257669772ab17add4fbd88a7b4981d0</t>
+    <t>c0cfb05785ba25feadb966caf1fa5a50</t>
   </si>
   <si>
     <t>fit</t>
@@ -320,13 +320,13 @@
     <t>03_Cluster_groups/Muscle_strength/03_Protein_Contrasts/c_data/fit.rds</t>
   </si>
   <si>
-    <t>4b3d729be71f7a7648f18f8a521ccc88</t>
-  </si>
-  <si>
-    <t>03_Cluster_groups/Muscle_strength/01_Clustering/c_data/inputs/DAList_limpa.rds</t>
-  </si>
-  <si>
-    <t>f650266fc408e16f3363512e5866142c</t>
+    <t>293a41d7ef36de7179b42dc1f593e3d3</t>
+  </si>
+  <si>
+    <t>01_Processing/03_Quantification/c_data/DAList_limpa.rds</t>
+  </si>
+  <si>
+    <t>268362b9975bc00d3bc3b85b0f5736f7</t>
   </si>
   <si>
     <t>phenotype</t>
